--- a/business_surveys/019_social_care_digital_transformation_survey--business_surveys.xlsx
+++ b/business_surveys/019_social_care_digital_transformation_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="49" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -548,14 +548,10 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Introduction and Background</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>This is background</t>
-        </is>
-      </c>
+          <t>Describe your experience with digital transformation in social care</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -565,7 +561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -575,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Background</t>
+          <t>Do you think digital transformation is beneficial for social care?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -598,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Introduction and Background</t>
+          <t>What are the main challenges for implementing digital transformation in social care?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -611,7 +607,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -621,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Introduction and Background</t>
+          <t>Do you think digital transformation can increase accessibility to social services?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -644,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Background</t>
+          <t>How do you see digital transformation affecting your work or daily life?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -667,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Introduction and Background</t>
+          <t>What are your thoughts on the importance of digital literacy in the context of social care?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -690,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Background</t>
+          <t>How do you see digital transformation impacting the relationships between social workers and clients?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -703,7 +699,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -713,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Introduction and Background</t>
+          <t>Do you think digital transformation can improve communication between social services and their clients?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -736,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Background</t>
+          <t>Are there any areas of social care that you think are not well-suited for digital transformation?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -759,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Introduction</t>
+          <t>What role do you think AI or machine learning can play in digital transformation in social care?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -772,7 +768,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -782,310 +778,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>What do you think about digital transformation?</t>
+          <t>Do you think digital transformation can lead to increased efficiency in social services?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>form_page_13</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>What do you think about digital transformation?</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>form_page_14</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>What do you think about digital transformation?</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>form_page_15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>What do you think about digital transformation?</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>form_page_16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Introduction</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>form_page_17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Introduction</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>form_page_18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Introduction</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>form_page_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Introduction</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>form_page_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Introduction</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>form_page_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>What do you think about digital transformation?</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>form_page_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>What do you think about digital transformation?</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>form_page_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>What do you think about digital transformation?</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>form_page_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>What do you think about digital transformation?</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>form_page_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Background</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1102,7 +799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1130,7 +827,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>form_page_16_choices</t>
+          <t>form_page_3_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1147,7 +844,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>form_page_16_choices</t>
+          <t>form_page_3_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1164,7 +861,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>form_page_16_choices</t>
+          <t>form_page_3_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1181,7 +878,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>form_page_16_choices</t>
+          <t>form_page_3_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1198,7 +895,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>form_page_16_choices</t>
+          <t>form_page_3_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1215,7 +912,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>form_page_17_choices</t>
+          <t>form_page_5_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1232,7 +929,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>form_page_17_choices</t>
+          <t>form_page_5_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1249,7 +946,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>form_page_17_choices</t>
+          <t>form_page_5_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1266,7 +963,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>form_page_17_choices</t>
+          <t>form_page_5_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1283,7 +980,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>form_page_17_choices</t>
+          <t>form_page_5_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1300,7 +997,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>form_page_18_choices</t>
+          <t>form_page_9_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1317,7 +1014,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>form_page_18_choices</t>
+          <t>form_page_9_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1334,7 +1031,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>form_page_18_choices</t>
+          <t>form_page_9_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1351,7 +1048,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>form_page_18_choices</t>
+          <t>form_page_9_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1368,7 +1065,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>form_page_18_choices</t>
+          <t>form_page_9_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1385,7 +1082,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>form_page_19_choices</t>
+          <t>form_page_12_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1402,7 +1099,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>form_page_19_choices</t>
+          <t>form_page_12_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1419,7 +1116,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>form_page_19_choices</t>
+          <t>form_page_12_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1436,7 +1133,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>form_page_19_choices</t>
+          <t>form_page_12_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1453,7 +1150,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>form_page_19_choices</t>
+          <t>form_page_12_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1462,431 +1159,6 @@
         </is>
       </c>
       <c r="C21" t="inlineStr">
-        <is>
-          <t>Strongly Agree</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>form_page_20_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>strongly_disagree</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Strongly Disagree</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>form_page_20_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>somewhat_disagree</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Somewhat Disagree</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>form_page_20_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>form_page_20_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>somewhat_agree</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Somewhat Agree</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>form_page_20_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>strongly_agree</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Strongly Agree</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>form_page_21_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>strongly_disagree</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Strongly Disagree</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>form_page_21_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>somewhat_disagree</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Somewhat Disagree</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>form_page_21_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>form_page_21_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>somewhat_agree</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Somewhat Agree</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>form_page_21_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>strongly_agree</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Strongly Agree</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>form_page_22_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>strongly_disagree</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Strongly Disagree</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>form_page_22_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>somewhat_disagree</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Somewhat Disagree</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>form_page_22_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>form_page_22_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>somewhat_agree</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Somewhat Agree</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>form_page_22_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>strongly_agree</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Strongly Agree</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>form_page_23_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>strongly_disagree</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Strongly Disagree</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>form_page_23_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>somewhat_disagree</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Somewhat Disagree</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>form_page_23_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>form_page_23_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>somewhat_agree</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Somewhat Agree</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>form_page_23_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>strongly_agree</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Strongly Agree</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>form_page_24_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>strongly_disagree</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Strongly Disagree</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>form_page_24_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>somewhat_disagree</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Somewhat Disagree</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>form_page_24_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>form_page_24_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>somewhat_agree</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Somewhat Agree</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>form_page_24_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>strongly_agree</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
         <is>
           <t>Strongly Agree</t>
         </is>
